--- a/shared network team Budget.xlsx
+++ b/shared network team Budget.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lilya\Desktop\Project 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D4C46C7-410F-40FA-B1F7-508D70AE487E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F1BEF0-C9DC-41F2-A1B6-4842710EA9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="30912" windowHeight="16752" xr2:uid="{58261409-75FE-4CCD-BF1A-46427F60D179}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{58261409-75FE-4CCD-BF1A-46427F60D179}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget sheet" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="68">
   <si>
     <t>Accounting code</t>
   </si>
@@ -116,9 +116,6 @@
     <t>printer0</t>
   </si>
   <si>
-    <t>LAN</t>
-  </si>
-  <si>
     <t>router1</t>
   </si>
   <si>
@@ -191,9 +188,6 @@
     <t>CLOUD-ISP</t>
   </si>
   <si>
-    <t>ISP</t>
-  </si>
-  <si>
     <t xml:space="preserve">Other </t>
   </si>
   <si>
@@ -225,6 +219,27 @@
   </si>
   <si>
     <t>cost 2euros per m, avg 2 m per connection, cat7- Ethernet cables (envelope)</t>
+  </si>
+  <si>
+    <t>Router2</t>
+  </si>
+  <si>
+    <t>LAN2</t>
+  </si>
+  <si>
+    <t>LAN1</t>
+  </si>
+  <si>
+    <t>NAT Router</t>
+  </si>
+  <si>
+    <t>NAT router</t>
+  </si>
+  <si>
+    <t>ISP - not counted as outside of internal network</t>
+  </si>
+  <si>
+    <t>STMP Server</t>
   </si>
 </sst>
 </file>
@@ -572,97 +587,97 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="165" fontId="3" fillId="2" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma 2 3" xfId="3" xr:uid="{813095FF-7F44-43B3-8E3E-7506F53FA7FF}"/>
@@ -1000,7 +1015,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{032A4627-C2A2-4924-A3A7-17B2D83EA8DD}">
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.77734375" bestFit="1" customWidth="1"/>
@@ -1051,11 +1066,11 @@
       <c r="L2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="25" t="s">
+      <c r="M2" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="27" t="s">
-        <v>29</v>
+      <c r="N2" s="14" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -1063,7 +1078,7 @@
         <v>13000</v>
       </c>
       <c r="B3" s="10" t="str">
-        <f>LOOKUP(A3,$B$46:$B$52,$C$46:$C$52)</f>
+        <f t="shared" ref="B3:B38" si="0">LOOKUP(A3,$B$51:$B$57,$C$51:$C$57)</f>
         <v>IT - equipment - end users (computers and laptops)</v>
       </c>
       <c r="C3" s="10" t="s">
@@ -1073,7 +1088,7 @@
         <v>23</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F3" s="10"/>
       <c r="G3" s="10">
@@ -1091,11 +1106,11 @@
       <c r="L3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M3" s="26">
+      <c r="M3" s="13">
         <v>150</v>
       </c>
       <c r="N3" s="10">
-        <f>M3*G3</f>
+        <f t="shared" ref="N3:N41" si="1">M3*G3</f>
         <v>750</v>
       </c>
     </row>
@@ -1104,7 +1119,7 @@
         <v>12000</v>
       </c>
       <c r="B4" s="10" t="str">
-        <f>LOOKUP(A4,$B$46:$B$52,$C$46:$C$52)</f>
+        <f t="shared" si="0"/>
         <v>IT - equipment - periphery (telephony and printers)</v>
       </c>
       <c r="C4" s="10" t="s">
@@ -1125,18 +1140,18 @@
       </c>
       <c r="I4" s="10"/>
       <c r="J4" s="10">
-        <f t="shared" ref="J4" si="0">G4*H4</f>
+        <f t="shared" ref="J4" si="2">G4*H4</f>
         <v>1500</v>
       </c>
       <c r="K4" s="10"/>
       <c r="L4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M4" s="26">
+      <c r="M4" s="13">
         <v>30</v>
       </c>
       <c r="N4" s="10">
-        <f>M4*G4</f>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
     </row>
@@ -1145,7 +1160,7 @@
         <v>12000</v>
       </c>
       <c r="B5" s="10" t="str">
-        <f>LOOKUP(A5,$B$46:$B$52,$C$46:$C$52)</f>
+        <f t="shared" si="0"/>
         <v>IT - equipment - periphery (telephony and printers)</v>
       </c>
       <c r="C5" s="10" t="s">
@@ -1166,18 +1181,18 @@
       </c>
       <c r="I5" s="10"/>
       <c r="J5" s="10">
-        <f t="shared" ref="J5:J36" si="1">G5*H5</f>
+        <f t="shared" ref="J5:J41" si="3">G5*H5</f>
         <v>75</v>
       </c>
       <c r="K5" s="10"/>
       <c r="L5" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M5" s="26">
+      <c r="M5" s="13">
         <v>10</v>
       </c>
       <c r="N5" s="10">
-        <f>M5*G5</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -1186,7 +1201,7 @@
         <v>11000</v>
       </c>
       <c r="B6" s="10" t="str">
-        <f>LOOKUP(A6,$B$46:$B$52,$C$46:$C$52)</f>
+        <f t="shared" si="0"/>
         <v>IT- equipment - switches</v>
       </c>
       <c r="C6" s="10" t="s">
@@ -1207,18 +1222,18 @@
       </c>
       <c r="I6" s="10"/>
       <c r="J6" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1500</v>
       </c>
       <c r="K6" s="10"/>
       <c r="L6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M6" s="26">
+      <c r="M6" s="13">
         <v>40</v>
       </c>
       <c r="N6" s="10">
-        <f>M6*G6</f>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
     </row>
@@ -1227,17 +1242,17 @@
         <v>12000</v>
       </c>
       <c r="B7" s="10" t="str">
-        <f>LOOKUP(A7,$B$46:$B$52,$C$46:$C$52)</f>
+        <f t="shared" si="0"/>
         <v>IT - equipment - periphery (telephony and printers)</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7" s="10"/>
       <c r="G7" s="10">
@@ -1248,18 +1263,18 @@
       </c>
       <c r="I7" s="10"/>
       <c r="J7" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>150</v>
       </c>
       <c r="K7" s="10"/>
       <c r="L7" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="M7" s="26">
+        <v>40</v>
+      </c>
+      <c r="M7" s="13">
         <v>35</v>
       </c>
       <c r="N7" s="10">
-        <f>M7*G7</f>
+        <f t="shared" si="1"/>
         <v>35</v>
       </c>
     </row>
@@ -1268,17 +1283,17 @@
         <v>10000</v>
       </c>
       <c r="B8" s="10" t="str">
-        <f>LOOKUP(A8,$B$46:$B$52,$C$46:$C$52)</f>
+        <f t="shared" si="0"/>
         <v>IT - equipment - routers</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8" s="10"/>
       <c r="G8" s="10">
@@ -1289,142 +1304,142 @@
       </c>
       <c r="I8" s="10"/>
       <c r="J8" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>150</v>
       </c>
       <c r="K8" s="10"/>
       <c r="L8" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M8" s="26">
+        <v>63</v>
+      </c>
+      <c r="M8" s="13">
         <v>35</v>
       </c>
       <c r="N8" s="10">
-        <f>M8*G8</f>
+        <f t="shared" si="1"/>
         <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="10">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="B9" s="10" t="str">
-        <f>LOOKUP(A9,$B$46:$B$52,$C$46:$C$52)</f>
-        <v>IT- equipment - switches</v>
+        <f t="shared" si="0"/>
+        <v>IT - equipment - routers</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="F9" s="10"/>
       <c r="G9" s="10">
         <v>1</v>
       </c>
       <c r="H9" s="10">
-        <v>1500</v>
+        <v>150</v>
       </c>
       <c r="I9" s="10"/>
       <c r="J9" s="10">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="3"/>
+        <v>150</v>
       </c>
       <c r="K9" s="10"/>
       <c r="L9" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M9" s="26">
-        <v>40</v>
+        <v>62</v>
+      </c>
+      <c r="M9" s="13">
+        <v>35</v>
       </c>
       <c r="N9" s="10">
-        <f>M9*G9</f>
-        <v>40</v>
+        <f t="shared" si="1"/>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
-        <v>13000</v>
+        <v>11000</v>
       </c>
       <c r="B10" s="10" t="str">
-        <f>LOOKUP(A10,$B$46:$B$52,$C$46:$C$52)</f>
-        <v>IT - equipment - end users (computers and laptops)</v>
+        <f t="shared" si="0"/>
+        <v>IT- equipment - switches</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F10" s="10"/>
       <c r="G10" s="10">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H10" s="10">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I10" s="10"/>
       <c r="J10" s="10">
-        <f t="shared" si="1"/>
-        <v>8000</v>
+        <f t="shared" si="3"/>
+        <v>1500</v>
       </c>
       <c r="K10" s="10"/>
       <c r="L10" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M10" s="26">
-        <v>150</v>
+        <v>31</v>
+      </c>
+      <c r="M10" s="13">
+        <v>40</v>
       </c>
       <c r="N10" s="10">
-        <f>M10*G10</f>
-        <v>1200</v>
+        <f t="shared" si="1"/>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="B11" s="10" t="str">
-        <f>LOOKUP(A11,$B$46:$B$52,$C$46:$C$52)</f>
-        <v>IT - equipment - periphery (telephony and printers)</v>
+        <f t="shared" si="0"/>
+        <v>IT - equipment - end users (computers and laptops)</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="F11" s="10"/>
       <c r="G11" s="10">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H11" s="10">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I11" s="10"/>
       <c r="J11" s="10">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="3"/>
+        <v>8000</v>
       </c>
       <c r="K11" s="10"/>
       <c r="L11" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M11" s="26">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="M11" s="13">
+        <v>150</v>
       </c>
       <c r="N11" s="10">
-        <f>M11*G11</f>
-        <v>30</v>
+        <f t="shared" si="1"/>
+        <v>1200</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1432,163 +1447,163 @@
         <v>12000</v>
       </c>
       <c r="B12" s="10" t="str">
-        <f>LOOKUP(A12,$B$46:$B$52,$C$46:$C$52)</f>
+        <f t="shared" si="0"/>
         <v>IT - equipment - periphery (telephony and printers)</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="10">
         <v>1</v>
       </c>
       <c r="H12" s="10">
-        <v>75</v>
+        <v>1500</v>
       </c>
       <c r="I12" s="10"/>
       <c r="J12" s="10">
-        <f t="shared" si="1"/>
-        <v>75</v>
+        <f t="shared" si="3"/>
+        <v>1500</v>
       </c>
       <c r="K12" s="10"/>
       <c r="L12" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M12" s="26">
-        <v>10</v>
+        <v>31</v>
+      </c>
+      <c r="M12" s="13">
+        <v>30</v>
       </c>
       <c r="N12" s="10">
-        <f>M12*G12</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="B13" s="10" t="str">
-        <f>LOOKUP(A13,$B$46:$B$52,$C$46:$C$52)</f>
-        <v>IT- equipment - switches</v>
+        <f t="shared" si="0"/>
+        <v>IT - equipment - periphery (telephony and printers)</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F13" s="10"/>
       <c r="G13" s="10">
         <v>1</v>
       </c>
       <c r="H13" s="10">
-        <v>1500</v>
+        <v>75</v>
       </c>
       <c r="I13" s="10"/>
       <c r="J13" s="10">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="3"/>
+        <v>75</v>
       </c>
       <c r="K13" s="10"/>
       <c r="L13" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="M13" s="26">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="M13" s="13">
+        <v>10</v>
       </c>
       <c r="N13" s="10">
-        <f>M13*G13</f>
-        <v>40</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
-        <v>13000</v>
+        <v>11000</v>
       </c>
       <c r="B14" s="10" t="str">
-        <f>LOOKUP(A14,$B$46:$B$52,$C$46:$C$52)</f>
-        <v>IT - equipment - end users (computers and laptops)</v>
+        <f t="shared" si="0"/>
+        <v>IT- equipment - switches</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F14" s="10"/>
       <c r="G14" s="10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H14" s="10">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I14" s="10"/>
       <c r="J14" s="10">
-        <f t="shared" si="1"/>
-        <v>10000</v>
+        <f t="shared" si="3"/>
+        <v>1500</v>
       </c>
       <c r="K14" s="10"/>
       <c r="L14" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="M14" s="26">
-        <v>150</v>
+        <v>34</v>
+      </c>
+      <c r="M14" s="13">
+        <v>40</v>
       </c>
       <c r="N14" s="10">
-        <f>M14*G14</f>
-        <v>1500</v>
+        <f t="shared" si="1"/>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="10">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="B15" s="10" t="str">
-        <f>LOOKUP(A15,$B$46:$B$52,$C$46:$C$52)</f>
-        <v>IT - equipment - periphery (telephony and printers)</v>
+        <f t="shared" si="0"/>
+        <v>IT - equipment - end users (computers and laptops)</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F15" s="10"/>
       <c r="G15" s="10">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H15" s="10">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="I15" s="10"/>
       <c r="J15" s="10">
-        <f t="shared" si="1"/>
-        <v>75</v>
+        <f t="shared" si="3"/>
+        <v>10000</v>
       </c>
       <c r="K15" s="10"/>
       <c r="L15" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="M15" s="26">
-        <v>10</v>
+        <v>34</v>
+      </c>
+      <c r="M15" s="13">
+        <v>150</v>
       </c>
       <c r="N15" s="10">
-        <f>M15*G15</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>1500</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1596,58 +1611,58 @@
         <v>12000</v>
       </c>
       <c r="B16" s="10" t="str">
-        <f>LOOKUP(A16,$B$46:$B$52,$C$46:$C$52)</f>
+        <f t="shared" si="0"/>
         <v>IT - equipment - periphery (telephony and printers)</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F16" s="10"/>
       <c r="G16" s="10">
         <v>1</v>
       </c>
       <c r="H16" s="10">
-        <v>1500</v>
+        <v>75</v>
       </c>
       <c r="I16" s="10"/>
       <c r="J16" s="10">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="3"/>
+        <v>75</v>
       </c>
       <c r="K16" s="10"/>
       <c r="L16" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="M16" s="26">
-        <v>30</v>
+        <v>34</v>
+      </c>
+      <c r="M16" s="13">
+        <v>10</v>
       </c>
       <c r="N16" s="10">
-        <f>M16*G16</f>
-        <v>30</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="10">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="B17" s="10" t="str">
-        <f>LOOKUP(A17,$B$46:$B$52,$C$46:$C$52)</f>
-        <v>IT- equipment - switches</v>
+        <f t="shared" si="0"/>
+        <v>IT - equipment - periphery (telephony and printers)</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="10">
@@ -1658,101 +1673,101 @@
       </c>
       <c r="I17" s="10"/>
       <c r="J17" s="10">
-        <f>G17*H17</f>
+        <f t="shared" si="3"/>
         <v>1500</v>
       </c>
       <c r="K17" s="10"/>
       <c r="L17" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="M17" s="26">
-        <v>40</v>
+        <v>34</v>
+      </c>
+      <c r="M17" s="13">
+        <v>30</v>
       </c>
       <c r="N17" s="10">
-        <f>M17*G17</f>
-        <v>40</v>
+        <f t="shared" si="1"/>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
-        <v>13000</v>
+        <v>11000</v>
       </c>
       <c r="B18" s="10" t="str">
-        <f>LOOKUP(A18,$B$46:$B$52,$C$46:$C$52)</f>
-        <v>IT - equipment - end users (computers and laptops)</v>
+        <f t="shared" si="0"/>
+        <v>IT- equipment - switches</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H18" s="10">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I18" s="10"/>
       <c r="J18" s="10">
-        <f t="shared" si="1"/>
-        <v>10000</v>
+        <f>G18*H18</f>
+        <v>1500</v>
       </c>
       <c r="K18" s="10"/>
       <c r="L18" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="M18" s="26">
-        <v>150</v>
+        <v>35</v>
+      </c>
+      <c r="M18" s="13">
+        <v>40</v>
       </c>
       <c r="N18" s="10">
-        <f>M18*G18</f>
-        <v>1500</v>
+        <f t="shared" si="1"/>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="B19" s="10" t="str">
-        <f>LOOKUP(A19,$B$46:$B$52,$C$46:$C$52)</f>
-        <v>IT - equipment - periphery (telephony and printers)</v>
+        <f t="shared" si="0"/>
+        <v>IT - equipment - end users (computers and laptops)</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="10">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H19" s="10">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="I19" s="10"/>
       <c r="J19" s="10">
-        <f t="shared" ref="J19:J20" si="2">G19*H19</f>
-        <v>75</v>
+        <f t="shared" si="3"/>
+        <v>10000</v>
       </c>
       <c r="K19" s="10"/>
       <c r="L19" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="M19" s="26">
-        <v>10</v>
+        <v>35</v>
+      </c>
+      <c r="M19" s="13">
+        <v>150</v>
       </c>
       <c r="N19" s="10">
-        <f>M19*G19</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>1500</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1760,58 +1775,58 @@
         <v>12000</v>
       </c>
       <c r="B20" s="10" t="str">
-        <f>LOOKUP(A20,$B$46:$B$52,$C$46:$C$52)</f>
+        <f t="shared" si="0"/>
         <v>IT - equipment - periphery (telephony and printers)</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="10">
         <v>1</v>
       </c>
       <c r="H20" s="10">
-        <v>1500</v>
+        <v>75</v>
       </c>
       <c r="I20" s="10"/>
       <c r="J20" s="10">
-        <f t="shared" si="2"/>
-        <v>1500</v>
+        <f t="shared" ref="J20:J21" si="4">G20*H20</f>
+        <v>75</v>
       </c>
       <c r="K20" s="10"/>
       <c r="L20" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="M20" s="26">
-        <v>30</v>
+        <v>35</v>
+      </c>
+      <c r="M20" s="13">
+        <v>10</v>
       </c>
       <c r="N20" s="10">
-        <f>M20*G20</f>
-        <v>30</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="B21" s="10" t="str">
-        <f>LOOKUP(A21,$B$46:$B$52,$C$46:$C$52)</f>
-        <v>IT- equipment - switches</v>
+        <f t="shared" si="0"/>
+        <v>IT - equipment - periphery (telephony and printers)</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="10">
@@ -1822,101 +1837,101 @@
       </c>
       <c r="I21" s="10"/>
       <c r="J21" s="10">
-        <f>G21*H21</f>
+        <f t="shared" si="4"/>
         <v>1500</v>
       </c>
       <c r="K21" s="10"/>
       <c r="L21" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="M21" s="26">
-        <v>40</v>
+        <v>35</v>
+      </c>
+      <c r="M21" s="13">
+        <v>30</v>
       </c>
       <c r="N21" s="10">
-        <f>M21*G21</f>
-        <v>40</v>
+        <f t="shared" si="1"/>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
-        <v>13000</v>
+        <v>11000</v>
       </c>
       <c r="B22" s="10" t="str">
-        <f>LOOKUP(A22,$B$46:$B$52,$C$46:$C$52)</f>
-        <v>IT - equipment - end users (computers and laptops)</v>
+        <f t="shared" si="0"/>
+        <v>IT- equipment - switches</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H22" s="10">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I22" s="10"/>
       <c r="J22" s="10">
-        <f t="shared" si="1"/>
-        <v>10000</v>
+        <f>G22*H22</f>
+        <v>1500</v>
       </c>
       <c r="K22" s="10"/>
       <c r="L22" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="M22" s="26">
-        <v>150</v>
+        <v>36</v>
+      </c>
+      <c r="M22" s="13">
+        <v>40</v>
       </c>
       <c r="N22" s="10">
-        <f>M22*G22</f>
-        <v>1500</v>
+        <f t="shared" si="1"/>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="10">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="B23" s="10" t="str">
-        <f>LOOKUP(A23,$B$46:$B$52,$C$46:$C$52)</f>
-        <v>IT - equipment - periphery (telephony and printers)</v>
+        <f t="shared" si="0"/>
+        <v>IT - equipment - end users (computers and laptops)</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="10">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H23" s="10">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="I23" s="10"/>
       <c r="J23" s="10">
-        <f t="shared" si="1"/>
-        <v>75</v>
+        <f t="shared" si="3"/>
+        <v>10000</v>
       </c>
       <c r="K23" s="10"/>
       <c r="L23" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="M23" s="26">
-        <v>10</v>
+        <v>36</v>
+      </c>
+      <c r="M23" s="13">
+        <v>150</v>
       </c>
       <c r="N23" s="10">
-        <f>M23*G23</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>1500</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -1924,58 +1939,58 @@
         <v>12000</v>
       </c>
       <c r="B24" s="10" t="str">
-        <f>LOOKUP(A24,$B$46:$B$52,$C$46:$C$52)</f>
+        <f t="shared" si="0"/>
         <v>IT - equipment - periphery (telephony and printers)</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="10">
         <v>1</v>
       </c>
       <c r="H24" s="10">
-        <v>1500</v>
+        <v>75</v>
       </c>
       <c r="I24" s="10"/>
       <c r="J24" s="10">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="3"/>
+        <v>75</v>
       </c>
       <c r="K24" s="10"/>
       <c r="L24" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="M24" s="26">
-        <v>30</v>
+        <v>36</v>
+      </c>
+      <c r="M24" s="13">
+        <v>10</v>
       </c>
       <c r="N24" s="10">
-        <f>M24*G24</f>
-        <v>30</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="10">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="B25" s="10" t="str">
-        <f>LOOKUP(A25,$B$46:$B$52,$C$46:$C$52)</f>
-        <v>IT- equipment - switches</v>
+        <f t="shared" si="0"/>
+        <v>IT - equipment - periphery (telephony and printers)</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="10">
@@ -1986,101 +2001,101 @@
       </c>
       <c r="I25" s="10"/>
       <c r="J25" s="10">
-        <f>G25*H25</f>
+        <f t="shared" si="3"/>
         <v>1500</v>
       </c>
       <c r="K25" s="10"/>
       <c r="L25" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M25" s="26">
-        <v>40</v>
+        <v>36</v>
+      </c>
+      <c r="M25" s="13">
+        <v>30</v>
       </c>
       <c r="N25" s="10">
-        <f>M25*G25</f>
-        <v>40</v>
+        <f t="shared" si="1"/>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
-        <v>13000</v>
+        <v>11000</v>
       </c>
       <c r="B26" s="10" t="str">
-        <f>LOOKUP(A26,$B$46:$B$52,$C$46:$C$52)</f>
-        <v>IT - equipment - end users (computers and laptops)</v>
+        <f t="shared" si="0"/>
+        <v>IT- equipment - switches</v>
       </c>
       <c r="C26" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="F26" s="10"/>
       <c r="G26" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H26" s="10">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I26" s="10"/>
       <c r="J26" s="10">
-        <f t="shared" si="1"/>
-        <v>5000</v>
+        <f>G26*H26</f>
+        <v>1500</v>
       </c>
       <c r="K26" s="10"/>
       <c r="L26" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M26" s="26">
-        <v>150</v>
+        <v>37</v>
+      </c>
+      <c r="M26" s="13">
+        <v>40</v>
       </c>
       <c r="N26" s="10">
-        <f>M26*G26</f>
-        <v>750</v>
+        <f t="shared" si="1"/>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="B27" s="10" t="str">
-        <f>LOOKUP(A27,$B$46:$B$52,$C$46:$C$52)</f>
-        <v>IT - equipment - periphery (telephony and printers)</v>
+        <f t="shared" si="0"/>
+        <v>IT - equipment - end users (computers and laptops)</v>
       </c>
       <c r="C27" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F27" s="10"/>
       <c r="G27" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H27" s="10">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" s="10">
-        <f t="shared" si="1"/>
-        <v>75</v>
+        <f t="shared" si="3"/>
+        <v>5000</v>
       </c>
       <c r="K27" s="10"/>
       <c r="L27" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M27" s="26">
-        <v>10</v>
+        <v>37</v>
+      </c>
+      <c r="M27" s="13">
+        <v>150</v>
       </c>
       <c r="N27" s="10">
-        <f>M27*G27</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>750</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -2088,163 +2103,163 @@
         <v>12000</v>
       </c>
       <c r="B28" s="10" t="str">
-        <f>LOOKUP(A28,$B$46:$B$52,$C$46:$C$52)</f>
+        <f t="shared" si="0"/>
         <v>IT - equipment - periphery (telephony and printers)</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F28" s="10"/>
       <c r="G28" s="10">
         <v>1</v>
       </c>
       <c r="H28" s="10">
-        <v>1500</v>
+        <v>75</v>
       </c>
       <c r="I28" s="10"/>
       <c r="J28" s="10">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="3"/>
+        <v>75</v>
       </c>
       <c r="K28" s="10"/>
       <c r="L28" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M28" s="26">
-        <v>30</v>
+        <v>37</v>
+      </c>
+      <c r="M28" s="13">
+        <v>10</v>
       </c>
       <c r="N28" s="10">
-        <f>M28*G28</f>
-        <v>30</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="B29" s="10" t="str">
-        <f>LOOKUP(A29,$B$46:$B$52,$C$46:$C$52)</f>
-        <v>IT - equipment - routers</v>
+        <f t="shared" si="0"/>
+        <v>IT - equipment - periphery (telephony and printers)</v>
       </c>
       <c r="C29" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="F29" s="10"/>
       <c r="G29" s="10">
         <v>1</v>
       </c>
       <c r="H29" s="10">
-        <v>100</v>
+        <v>1500</v>
       </c>
       <c r="I29" s="10"/>
       <c r="J29" s="10">
-        <f t="shared" si="1"/>
-        <v>100</v>
+        <f t="shared" si="3"/>
+        <v>1500</v>
       </c>
       <c r="K29" s="10"/>
       <c r="L29" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="M29" s="26">
-        <v>50</v>
+        <v>37</v>
+      </c>
+      <c r="M29" s="13">
+        <v>30</v>
       </c>
       <c r="N29" s="10">
-        <f>M29*G29</f>
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="B30" s="10" t="str">
-        <f>LOOKUP(A30,$B$46:$B$52,$C$46:$C$52)</f>
-        <v>IT- equipment - switches</v>
+        <f t="shared" si="0"/>
+        <v>IT - equipment - routers</v>
       </c>
       <c r="C30" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F30" s="10"/>
       <c r="G30" s="10">
         <v>1</v>
       </c>
       <c r="H30" s="10">
-        <v>1500</v>
+        <v>100</v>
       </c>
       <c r="I30" s="10"/>
       <c r="J30" s="10">
-        <f>G30*H30</f>
-        <v>1500</v>
+        <f t="shared" si="3"/>
+        <v>100</v>
       </c>
       <c r="K30" s="10"/>
       <c r="L30" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="M30" s="26">
-        <v>40</v>
+        <v>57</v>
+      </c>
+      <c r="M30" s="13">
+        <v>50</v>
       </c>
       <c r="N30" s="10">
-        <f>M30*G30</f>
-        <v>40</v>
+        <f t="shared" si="1"/>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
-        <v>15000</v>
+        <v>11000</v>
       </c>
       <c r="B31" s="10" t="str">
-        <f>LOOKUP(A31,$B$46:$B$52,$C$46:$C$52)</f>
-        <v>IT - equipment - servers</v>
+        <f t="shared" si="0"/>
+        <v>IT- equipment - switches</v>
       </c>
       <c r="C31" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F31" s="10"/>
       <c r="G31" s="10">
         <v>1</v>
       </c>
       <c r="H31" s="10">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I31" s="10"/>
       <c r="J31" s="10">
-        <f t="shared" si="1"/>
-        <v>2000</v>
+        <f>G31*H31</f>
+        <v>1500</v>
       </c>
       <c r="K31" s="10"/>
       <c r="L31" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="M31" s="26">
-        <v>200</v>
+        <v>46</v>
+      </c>
+      <c r="M31" s="13">
+        <v>40</v>
       </c>
       <c r="N31" s="10">
-        <f>M31*G31</f>
-        <v>200</v>
+        <f t="shared" si="1"/>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -2252,17 +2267,17 @@
         <v>15000</v>
       </c>
       <c r="B32" s="10" t="str">
-        <f>LOOKUP(A32,$B$46:$B$52,$C$46:$C$52)</f>
+        <f t="shared" si="0"/>
         <v>IT - equipment - servers</v>
       </c>
       <c r="C32" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F32" s="10"/>
       <c r="G32" s="10">
@@ -2273,508 +2288,661 @@
       </c>
       <c r="I32" s="10"/>
       <c r="J32" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2000</v>
       </c>
       <c r="K32" s="10"/>
       <c r="L32" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="M32" s="26">
+        <v>46</v>
+      </c>
+      <c r="M32" s="13">
         <v>200</v>
       </c>
       <c r="N32" s="10">
-        <f>M32*G32</f>
+        <f t="shared" si="1"/>
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
-        <v>14000</v>
+        <v>15000</v>
       </c>
       <c r="B33" s="10" t="str">
-        <f>LOOKUP(A33,$B$46:$B$52,$C$46:$C$52)</f>
-        <v xml:space="preserve">IT - equipment - cables </v>
+        <f t="shared" si="0"/>
+        <v>IT - equipment - servers</v>
       </c>
       <c r="C33" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="10">
-        <f>10*10*G33</f>
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="I33" s="10"/>
       <c r="J33" s="10">
-        <f t="shared" si="1"/>
-        <v>400</v>
+        <f t="shared" si="3"/>
+        <v>2000</v>
       </c>
       <c r="K33" s="10"/>
       <c r="L33" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="M33" s="26">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="M33" s="13">
+        <v>200</v>
       </c>
       <c r="N33" s="10">
-        <f>M33*G33</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>14000</v>
       </c>
       <c r="B34" s="10" t="str">
-        <f>LOOKUP(A34,$B$46:$B$52,$C$46:$C$52)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">IT - equipment - cables </v>
       </c>
       <c r="C34" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="10">
+        <v>2</v>
+      </c>
+      <c r="H34" s="10">
+        <f>10*10*G34</f>
+        <v>200</v>
+      </c>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10">
+        <f t="shared" si="3"/>
+        <v>400</v>
+      </c>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="M34" s="13">
+        <v>0</v>
+      </c>
+      <c r="N34" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="10">
+        <v>14000</v>
+      </c>
+      <c r="B35" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">IT - equipment - cables </v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10">
         <f>62+7</f>
         <v>69</v>
       </c>
-      <c r="H34" s="10">
-        <f>2*2*G34</f>
+      <c r="H35" s="10">
+        <f>2*2*G35</f>
         <v>276</v>
-      </c>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10">
-        <f t="shared" si="1"/>
-        <v>19044</v>
-      </c>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="M34" s="26">
-        <v>0</v>
-      </c>
-      <c r="N34" s="10">
-        <f>M34*G34</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" s="10">
-        <v>15001</v>
-      </c>
-      <c r="B35" s="10" t="str">
-        <f>LOOKUP(A35,$B$46:$B$52,$C$46:$C$52)</f>
-        <v xml:space="preserve">Other </v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10">
-        <v>1</v>
-      </c>
-      <c r="H35" s="10">
-        <v>1000</v>
       </c>
       <c r="I35" s="10"/>
       <c r="J35" s="10">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <f t="shared" si="3"/>
+        <v>19044</v>
       </c>
       <c r="K35" s="10"/>
       <c r="L35" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="M35" s="26">
+        <v>60</v>
+      </c>
+      <c r="M35" s="13">
         <v>0</v>
       </c>
       <c r="N35" s="10">
-        <f>M35*G35</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
-        <v>15001</v>
+        <v>10000</v>
       </c>
       <c r="B36" s="10" t="str">
-        <f>LOOKUP(A36,$B$46:$B$52,$C$46:$C$52)</f>
-        <v xml:space="preserve">Other </v>
+        <f t="shared" si="0"/>
+        <v>IT - equipment - routers</v>
       </c>
       <c r="C36" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="10">
         <v>1</v>
       </c>
       <c r="H36" s="10">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="I36" s="10"/>
       <c r="J36" s="10">
-        <f t="shared" si="1"/>
-        <v>5000</v>
+        <f t="shared" si="3"/>
+        <v>1000</v>
       </c>
       <c r="K36" s="10"/>
       <c r="L36" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="M36" s="26">
+        <v>65</v>
+      </c>
+      <c r="M36" s="13">
+        <v>40</v>
+      </c>
+      <c r="N36" s="10">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="10">
+        <v>15001</v>
+      </c>
+      <c r="B37" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Other </v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10">
+        <v>4</v>
+      </c>
+      <c r="H37" s="10">
+        <v>1000</v>
+      </c>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10">
+        <f t="shared" si="3"/>
+        <v>4000</v>
+      </c>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="M37" s="13">
+        <v>0</v>
+      </c>
+      <c r="N37" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" s="10">
+        <v>15000</v>
+      </c>
+      <c r="B38" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>IT - equipment - servers</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10">
+        <v>1</v>
+      </c>
+      <c r="H38" s="10">
+        <v>2000</v>
+      </c>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10">
+        <f t="shared" si="3"/>
+        <v>2000</v>
+      </c>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="M38" s="13">
+        <v>200</v>
+      </c>
+      <c r="N38" s="10">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="10"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="10"/>
+      <c r="L39" s="10"/>
+      <c r="M39" s="13"/>
+      <c r="N39" s="10"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" s="10"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="13"/>
+      <c r="N40" s="10"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41" s="10">
+        <v>15001</v>
+      </c>
+      <c r="B41" s="10" t="str">
+        <f>LOOKUP(A41,$B$51:$B$57,$C$51:$C$57)</f>
+        <v xml:space="preserve">Other </v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10">
+        <v>1</v>
+      </c>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K41" s="10"/>
+      <c r="L41" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="M41" s="13">
         <v>500</v>
       </c>
-      <c r="N36" s="10">
-        <f>M36*G36</f>
+      <c r="N41" s="10">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M38">
-        <f>SUM(M3:M37)</f>
-        <v>2440</v>
-      </c>
-      <c r="N38">
-        <f>SUM(N3:N37)</f>
-        <v>8740</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="44" spans="1:15" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="33" t="s">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M43">
+        <f>SUM(M3:M42)</f>
+        <v>2715</v>
+      </c>
+      <c r="N43">
+        <f>SUM(N3:N42)</f>
+        <v>9015</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="49" spans="2:15" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B49" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C44" s="32" t="s">
+      <c r="C49" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D44" s="24" t="s">
+      <c r="D49" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="E49" s="35"/>
+      <c r="F49" s="36"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="I49" s="35"/>
+      <c r="J49" s="36"/>
+      <c r="K49" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="E44" s="21"/>
-      <c r="F44" s="31"/>
-      <c r="G44" s="35"/>
-      <c r="H44" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="I44" s="21"/>
-      <c r="J44" s="31"/>
-      <c r="K44" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="L44" s="22"/>
-      <c r="M44" s="23"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B45" s="3" t="s">
+      <c r="L49" s="32"/>
+      <c r="M49" s="33"/>
+    </row>
+    <row r="50" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B50" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C45" s="4"/>
-      <c r="D45" s="18">
-        <f>SUM(D46:F52)</f>
-        <v>97794</v>
-      </c>
-      <c r="E45" s="19"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="36"/>
-      <c r="H45" s="42" t="s">
+      <c r="C50" s="4"/>
+      <c r="D50" s="37">
+        <f>SUM(D51:F57)</f>
+        <v>98944</v>
+      </c>
+      <c r="E50" s="38"/>
+      <c r="F50" s="39"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="I45" s="39"/>
-      <c r="J45" s="40"/>
-      <c r="K45" s="18">
-        <f>SUM(K46:M52)</f>
-        <v>97794</v>
-      </c>
-      <c r="L45" s="19"/>
-      <c r="M45" s="28"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B46" s="1">
-        <v>10000</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D46" s="12">
-        <f>SUMIF($A:$A,$B46,$J:$J)</f>
-        <v>250</v>
-      </c>
-      <c r="E46" s="13"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="37"/>
-      <c r="H46" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I46" s="13"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="12">
-        <f>SUMIF($D:$D,H46,$J:$J)</f>
-        <v>8075</v>
-      </c>
-      <c r="L46" s="13"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="43"/>
-      <c r="O46" s="43"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B47" s="1">
-        <v>11000</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D47" s="12">
-        <f>SUMIF($A:$A,$B47,$J:$J)</f>
-        <v>10500</v>
-      </c>
-      <c r="E47" s="13"/>
-      <c r="F47" s="29"/>
-      <c r="G47" s="37"/>
-      <c r="H47" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="I47" s="13"/>
-      <c r="J47" s="29"/>
-      <c r="K47" s="12">
-        <f>SUMIF($D:$D,H47,$J:$J)</f>
-        <v>11075</v>
-      </c>
-      <c r="L47" s="13"/>
-      <c r="M47" s="29"/>
-      <c r="N47" s="43"/>
-      <c r="O47" s="43"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B48" s="1">
-        <v>12000</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" s="12">
-        <f>SUMIF($A:$A,$B48,$J:$J)</f>
-        <v>9600</v>
-      </c>
-      <c r="E48" s="13"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="37"/>
-      <c r="H48" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I48" s="13"/>
-      <c r="J48" s="29"/>
-      <c r="K48" s="12">
-        <f>SUMIF($D:$D,H48,$J:$J)</f>
-        <v>13075</v>
-      </c>
-      <c r="L48" s="13"/>
-      <c r="M48" s="29"/>
-      <c r="N48" s="43"/>
-      <c r="O48" s="43"/>
-    </row>
-    <row r="49" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B49" s="1">
-        <v>13000</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D49" s="12">
-        <f>SUMIF($A:$A,$B49,$J:$J)</f>
-        <v>48000</v>
-      </c>
-      <c r="E49" s="13"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="37"/>
-      <c r="H49" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="I49" s="13"/>
-      <c r="J49" s="29"/>
-      <c r="K49" s="12">
-        <f>SUMIF($D:$D,H49,$J:$J)</f>
-        <v>13075</v>
-      </c>
-      <c r="L49" s="13"/>
-      <c r="M49" s="29"/>
-      <c r="N49" s="43"/>
-      <c r="O49" s="43"/>
-    </row>
-    <row r="50" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B50" s="1">
-        <v>14000</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D50" s="12">
-        <f>SUMIF($A:$A,$B50,$J:$J)</f>
-        <v>19444</v>
-      </c>
-      <c r="E50" s="13"/>
-      <c r="F50" s="29"/>
-      <c r="G50" s="37"/>
-      <c r="H50" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="I50" s="13"/>
-      <c r="J50" s="29"/>
-      <c r="K50" s="12">
-        <f>SUMIF($D:$D,H50,$J:$J)</f>
-        <v>13075</v>
-      </c>
-      <c r="L50" s="13"/>
-      <c r="M50" s="29"/>
-      <c r="N50" s="43"/>
-      <c r="O50" s="43"/>
+      <c r="I50" s="41"/>
+      <c r="J50" s="42"/>
+      <c r="K50" s="37">
+        <f>SUM(K51:M57)</f>
+        <v>98944</v>
+      </c>
+      <c r="L50" s="38"/>
+      <c r="M50" s="39"/>
     </row>
     <row r="51" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B51" s="1">
+        <v>10000</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" s="23">
+        <f t="shared" ref="D51:D57" si="5">SUMIF($A:$A,$B51,$J:$J)</f>
+        <v>1400</v>
+      </c>
+      <c r="E51" s="24"/>
+      <c r="F51" s="25"/>
+      <c r="G51" s="20"/>
+      <c r="H51" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="I51" s="24"/>
+      <c r="J51" s="25"/>
+      <c r="K51" s="23">
+        <f t="shared" ref="K51:K57" si="6">SUMIF($D:$D,H51,$J:$J)</f>
+        <v>8075</v>
+      </c>
+      <c r="L51" s="24"/>
+      <c r="M51" s="25"/>
+      <c r="N51" s="44"/>
+      <c r="O51" s="44"/>
+    </row>
+    <row r="52" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B52" s="1">
+        <v>11000</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" s="23">
+        <f t="shared" si="5"/>
+        <v>10500</v>
+      </c>
+      <c r="E52" s="24"/>
+      <c r="F52" s="25"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="I52" s="24"/>
+      <c r="J52" s="25"/>
+      <c r="K52" s="23">
+        <f t="shared" si="6"/>
+        <v>11075</v>
+      </c>
+      <c r="L52" s="24"/>
+      <c r="M52" s="25"/>
+      <c r="N52" s="44"/>
+      <c r="O52" s="44"/>
+    </row>
+    <row r="53" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B53" s="1">
+        <v>12000</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" s="23">
+        <f t="shared" si="5"/>
+        <v>9600</v>
+      </c>
+      <c r="E53" s="24"/>
+      <c r="F53" s="25"/>
+      <c r="G53" s="20"/>
+      <c r="H53" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="I53" s="24"/>
+      <c r="J53" s="25"/>
+      <c r="K53" s="23">
+        <f t="shared" si="6"/>
+        <v>13075</v>
+      </c>
+      <c r="L53" s="24"/>
+      <c r="M53" s="25"/>
+      <c r="N53" s="44"/>
+      <c r="O53" s="44"/>
+    </row>
+    <row r="54" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B54" s="1">
+        <v>13000</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" s="23">
+        <f t="shared" si="5"/>
+        <v>48000</v>
+      </c>
+      <c r="E54" s="24"/>
+      <c r="F54" s="25"/>
+      <c r="G54" s="20"/>
+      <c r="H54" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="I54" s="24"/>
+      <c r="J54" s="25"/>
+      <c r="K54" s="23">
+        <f t="shared" si="6"/>
+        <v>13075</v>
+      </c>
+      <c r="L54" s="24"/>
+      <c r="M54" s="25"/>
+      <c r="N54" s="44"/>
+      <c r="O54" s="44"/>
+    </row>
+    <row r="55" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B55" s="1">
+        <v>14000</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D55" s="23">
+        <f t="shared" si="5"/>
+        <v>19444</v>
+      </c>
+      <c r="E55" s="24"/>
+      <c r="F55" s="25"/>
+      <c r="G55" s="20"/>
+      <c r="H55" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="I55" s="24"/>
+      <c r="J55" s="25"/>
+      <c r="K55" s="23">
+        <f t="shared" si="6"/>
+        <v>13075</v>
+      </c>
+      <c r="L55" s="24"/>
+      <c r="M55" s="25"/>
+      <c r="N55" s="44"/>
+      <c r="O55" s="44"/>
+    </row>
+    <row r="56" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B56" s="1">
         <v>15000</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C56" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D51" s="12">
-        <f>SUMIF($A:$A,$B51,$J:$J)</f>
+      <c r="D56" s="23">
+        <f t="shared" si="5"/>
+        <v>6000</v>
+      </c>
+      <c r="E56" s="24"/>
+      <c r="F56" s="25"/>
+      <c r="G56" s="20"/>
+      <c r="H56" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="I56" s="24"/>
+      <c r="J56" s="25"/>
+      <c r="K56" s="23">
+        <f t="shared" si="6"/>
+        <v>12075</v>
+      </c>
+      <c r="L56" s="24"/>
+      <c r="M56" s="25"/>
+      <c r="N56" s="44"/>
+      <c r="O56" s="44"/>
+    </row>
+    <row r="57" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B57" s="1">
+        <v>15001</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D57" s="23">
+        <f t="shared" si="5"/>
         <v>4000</v>
       </c>
-      <c r="E51" s="13"/>
-      <c r="F51" s="29"/>
-      <c r="G51" s="37"/>
-      <c r="H51" s="12" t="s">
+      <c r="E57" s="24"/>
+      <c r="F57" s="25"/>
+      <c r="G57" s="20"/>
+      <c r="H57" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="I51" s="13"/>
-      <c r="J51" s="29"/>
-      <c r="K51" s="12">
-        <f>SUMIF($D:$D,H51,$J:$J)</f>
-        <v>9075</v>
-      </c>
-      <c r="L51" s="13"/>
-      <c r="M51" s="29"/>
-      <c r="N51" s="43"/>
-      <c r="O51" s="43"/>
-    </row>
-    <row r="52" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="1">
-        <v>15001</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D52" s="12">
-        <f>SUMIF($A:$A,$B52,$J:$J)</f>
-        <v>6000</v>
-      </c>
-      <c r="E52" s="13"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="37"/>
-      <c r="H52" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="I52" s="13"/>
-      <c r="J52" s="29"/>
-      <c r="K52" s="12">
-        <f>SUMIF($D:$D,H52,$J:$J)</f>
-        <v>30344</v>
-      </c>
-      <c r="L52" s="13"/>
-      <c r="M52" s="29"/>
-      <c r="N52" s="43"/>
-      <c r="O52" s="43"/>
-    </row>
-    <row r="53" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="16" t="s">
+      <c r="I57" s="24"/>
+      <c r="J57" s="25"/>
+      <c r="K57" s="23">
+        <f t="shared" si="6"/>
+        <v>28494</v>
+      </c>
+      <c r="L57" s="24"/>
+      <c r="M57" s="25"/>
+      <c r="N57" s="44"/>
+      <c r="O57" s="44"/>
+    </row>
+    <row r="58" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B58" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="C53" s="17"/>
-      <c r="D53" s="14">
-        <f>SUM(D46:F52)</f>
-        <v>97794</v>
-      </c>
-      <c r="E53" s="15"/>
-      <c r="F53" s="30"/>
-      <c r="G53" s="38"/>
-      <c r="H53" s="5"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="41"/>
-      <c r="K53" s="14">
-        <f>SUM(K45)</f>
-        <v>97794</v>
-      </c>
-      <c r="L53" s="15"/>
-      <c r="M53" s="30"/>
-      <c r="O53" s="44">
-        <f>K53-D53</f>
+      <c r="C58" s="30"/>
+      <c r="D58" s="26">
+        <f>SUM(D51:F57)</f>
+        <v>98944</v>
+      </c>
+      <c r="E58" s="27"/>
+      <c r="F58" s="28"/>
+      <c r="G58" s="21"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="15"/>
+      <c r="K58" s="26">
+        <f>SUM(K50)</f>
+        <v>98944</v>
+      </c>
+      <c r="L58" s="27"/>
+      <c r="M58" s="28"/>
+      <c r="O58" s="22">
+        <f>K58-D58</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="H44:J44"/>
-    <mergeCell ref="N48:O48"/>
-    <mergeCell ref="N47:O47"/>
-    <mergeCell ref="N46:O46"/>
+    <mergeCell ref="H49:J49"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="H57:J57"/>
+    <mergeCell ref="H56:J56"/>
+    <mergeCell ref="H55:J55"/>
+    <mergeCell ref="H54:J54"/>
+    <mergeCell ref="H53:J53"/>
     <mergeCell ref="H52:J52"/>
     <mergeCell ref="H51:J51"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="H49:J49"/>
-    <mergeCell ref="H48:J48"/>
-    <mergeCell ref="H47:J47"/>
-    <mergeCell ref="H46:J46"/>
-    <mergeCell ref="K51:M51"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="N51:O51"/>
-    <mergeCell ref="N50:O50"/>
-    <mergeCell ref="N49:O49"/>
-    <mergeCell ref="K44:M44"/>
-    <mergeCell ref="K47:M47"/>
-    <mergeCell ref="K48:M48"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="K56:M56"/>
+    <mergeCell ref="N57:O57"/>
+    <mergeCell ref="N56:O56"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="K49:M49"/>
+    <mergeCell ref="K52:M52"/>
+    <mergeCell ref="K53:M53"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D54:F54"/>
     <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="K45:M45"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="K46:M46"/>
     <mergeCell ref="D50:F50"/>
     <mergeCell ref="K50:M50"/>
-    <mergeCell ref="K49:M49"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="K52:M52"/>
-    <mergeCell ref="K53:M53"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="K51:M51"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="K55:M55"/>
+    <mergeCell ref="K54:M54"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="K57:M57"/>
+    <mergeCell ref="K58:M58"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="D58:F58"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/shared network team Budget.xlsx
+++ b/shared network team Budget.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lilya\Desktop\Project 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F1BEF0-C9DC-41F2-A1B6-4842710EA9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15EAEDB9-CF92-4D94-89BA-E63A5A63CDFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{58261409-75FE-4CCD-BF1A-46427F60D179}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget sheet" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Budget sheet'!$A$15:$O$53</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="73">
   <si>
     <t>Accounting code</t>
   </si>
@@ -240,6 +243,21 @@
   </si>
   <si>
     <t>STMP Server</t>
+  </si>
+  <si>
+    <t>VOICE</t>
+  </si>
+  <si>
+    <t>VOICE VOIP telephony</t>
+  </si>
+  <si>
+    <t>AAA Server</t>
+  </si>
+  <si>
+    <t>FTP Server</t>
+  </si>
+  <si>
+    <t>Secure servers</t>
   </si>
 </sst>
 </file>
@@ -1015,7 +1033,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{032A4627-C2A2-4924-A3A7-17B2D83EA8DD}">
-  <dimension ref="A1:O58"/>
+  <dimension ref="A1:O72"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.77734375" bestFit="1" customWidth="1"/>
@@ -1032,619 +1050,333 @@
     <col min="14" max="14" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:14" s="7" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:15" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="35"/>
+      <c r="F2" s="36"/>
+      <c r="H2" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="I2" s="35"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="32"/>
+      <c r="M2" s="33"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="37">
+        <f>SUM(D4:F10)</f>
+        <v>106180</v>
+      </c>
+      <c r="E3" s="38"/>
+      <c r="F3" s="39"/>
+      <c r="H3" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="41"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="37">
+        <f>SUM(K4:M10)</f>
+        <v>106180</v>
+      </c>
+      <c r="L3" s="38"/>
+      <c r="M3" s="39"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B4" s="1">
+        <v>10000</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="23">
+        <f>SUMIF($A:$A,$B4,$J:$J)</f>
+        <v>2580</v>
+      </c>
+      <c r="E4" s="24"/>
+      <c r="F4" s="25"/>
+      <c r="H4" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="24"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="23">
+        <f>SUMIF($D:$D,H4,$J:$J)</f>
+        <v>8075</v>
+      </c>
+      <c r="L4" s="24"/>
+      <c r="M4" s="25"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <v>11000</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="23">
+        <f>SUMIF($A:$A,$B5,$J:$J)</f>
+        <v>12000</v>
+      </c>
+      <c r="E5" s="24"/>
+      <c r="F5" s="25"/>
+      <c r="H5" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="24"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="23">
+        <f>SUMIF($D:$D,H5,$J:$J)</f>
+        <v>11075</v>
+      </c>
+      <c r="L5" s="24"/>
+      <c r="M5" s="25"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B6" s="1">
+        <v>12000</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="23">
+        <f>SUMIF($A:$A,$B6,$J:$J)</f>
+        <v>9600</v>
+      </c>
+      <c r="E6" s="24"/>
+      <c r="F6" s="25"/>
+      <c r="H6" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="24"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="23">
+        <f>SUMIF($D:$D,H6,$J:$J)</f>
+        <v>13075</v>
+      </c>
+      <c r="L6" s="24"/>
+      <c r="M6" s="25"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B7" s="1">
+        <v>13000</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="23">
+        <f>SUMIF($A:$A,$B7,$J:$J)</f>
+        <v>48000</v>
+      </c>
+      <c r="E7" s="24"/>
+      <c r="F7" s="25"/>
+      <c r="H7" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="24"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="23">
+        <f>SUMIF($D:$D,H7,$J:$J)</f>
+        <v>13075</v>
+      </c>
+      <c r="L7" s="24"/>
+      <c r="M7" s="25"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B8" s="1">
+        <v>14000</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="23">
+        <f>SUMIF($A:$A,$B8,$J:$J)</f>
+        <v>20000</v>
+      </c>
+      <c r="E8" s="24"/>
+      <c r="F8" s="25"/>
+      <c r="H8" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" s="24"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="23">
+        <f>SUMIF($D:$D,H8,$J:$J)</f>
+        <v>13075</v>
+      </c>
+      <c r="L8" s="24"/>
+      <c r="M8" s="25"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B9" s="1">
+        <v>15000</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="23">
+        <f>SUMIF($A:$A,$B9,$J:$J)</f>
+        <v>10000</v>
+      </c>
+      <c r="E9" s="24"/>
+      <c r="F9" s="25"/>
+      <c r="H9" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" s="24"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="23">
+        <f>SUMIF($D:$D,H9,$J:$J)</f>
+        <v>12075</v>
+      </c>
+      <c r="L9" s="24"/>
+      <c r="M9" s="25"/>
+    </row>
+    <row r="10" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="1">
+        <v>15001</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="23">
+        <f>SUMIF($A:$A,$B10,$J:$J)</f>
+        <v>4000</v>
+      </c>
+      <c r="E10" s="24"/>
+      <c r="F10" s="25"/>
+      <c r="H10" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="I10" s="24"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="23">
+        <f>SUMIF($D:$D,H10,$J:$J)</f>
+        <v>35730</v>
+      </c>
+      <c r="L10" s="24"/>
+      <c r="M10" s="25"/>
+    </row>
+    <row r="11" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="30"/>
+      <c r="D11" s="26">
+        <f>SUM(D4:F10)</f>
+        <v>106180</v>
+      </c>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="26">
+        <f>SUM(K3)</f>
+        <v>106180</v>
+      </c>
+      <c r="L11" s="27"/>
+      <c r="M11" s="28"/>
+      <c r="O11" s="22">
+        <f>K11-D11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="15" spans="1:15" s="7" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B15" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C15" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D15" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E15" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9" t="s">
+      <c r="F15" s="9"/>
+      <c r="G15" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H15" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I15" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J15" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9" t="s">
+      <c r="K15" s="9"/>
+      <c r="L15" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M15" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="N15" s="14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="10">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" s="10">
         <v>13000</v>
       </c>
-      <c r="B3" s="10" t="str">
-        <f t="shared" ref="B3:B38" si="0">LOOKUP(A3,$B$51:$B$57,$C$51:$C$57)</f>
+      <c r="B16" s="10" t="str">
+        <f t="shared" ref="B16:B54" si="0">LOOKUP(A16,$B$4:$B$10,$C$4:$C$10)</f>
         <v>IT - equipment - end users (computers and laptops)</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="10" t="s">
+      <c r="C16" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E16" s="10" t="s">
         <v>27</v>
-      </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10">
-        <v>5</v>
-      </c>
-      <c r="H3" s="10">
-        <v>1000</v>
-      </c>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10">
-        <f>G3*H3</f>
-        <v>5000</v>
-      </c>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" s="13">
-        <v>150</v>
-      </c>
-      <c r="N3" s="10">
-        <f t="shared" ref="N3:N41" si="1">M3*G3</f>
-        <v>750</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="10">
-        <v>12000</v>
-      </c>
-      <c r="B4" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>IT - equipment - periphery (telephony and printers)</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10">
-        <v>1</v>
-      </c>
-      <c r="H4" s="10">
-        <v>1500</v>
-      </c>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10">
-        <f t="shared" ref="J4" si="2">G4*H4</f>
-        <v>1500</v>
-      </c>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="M4" s="13">
-        <v>30</v>
-      </c>
-      <c r="N4" s="10">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="10">
-        <v>12000</v>
-      </c>
-      <c r="B5" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>IT - equipment - periphery (telephony and printers)</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10">
-        <v>1</v>
-      </c>
-      <c r="H5" s="10">
-        <v>75</v>
-      </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10">
-        <f t="shared" ref="J5:J41" si="3">G5*H5</f>
-        <v>75</v>
-      </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="M5" s="13">
-        <v>10</v>
-      </c>
-      <c r="N5" s="10">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="10">
-        <v>11000</v>
-      </c>
-      <c r="B6" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>IT- equipment - switches</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10">
-        <v>1</v>
-      </c>
-      <c r="H6" s="10">
-        <v>1500</v>
-      </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10">
-        <f t="shared" si="3"/>
-        <v>1500</v>
-      </c>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="M6" s="13">
-        <v>40</v>
-      </c>
-      <c r="N6" s="10">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="10">
-        <v>12000</v>
-      </c>
-      <c r="B7" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>IT - equipment - periphery (telephony and printers)</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10">
-        <v>1</v>
-      </c>
-      <c r="H7" s="10">
-        <v>150</v>
-      </c>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10">
-        <f t="shared" si="3"/>
-        <v>150</v>
-      </c>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="M7" s="13">
-        <v>35</v>
-      </c>
-      <c r="N7" s="10">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="10">
-        <v>10000</v>
-      </c>
-      <c r="B8" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>IT - equipment - routers</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10">
-        <v>1</v>
-      </c>
-      <c r="H8" s="10">
-        <v>150</v>
-      </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10">
-        <f t="shared" si="3"/>
-        <v>150</v>
-      </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="M8" s="13">
-        <v>35</v>
-      </c>
-      <c r="N8" s="10">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="10">
-        <v>10000</v>
-      </c>
-      <c r="B9" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>IT - equipment - routers</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10">
-        <v>1</v>
-      </c>
-      <c r="H9" s="10">
-        <v>150</v>
-      </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10">
-        <f t="shared" si="3"/>
-        <v>150</v>
-      </c>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="M9" s="13">
-        <v>35</v>
-      </c>
-      <c r="N9" s="10">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="10">
-        <v>11000</v>
-      </c>
-      <c r="B10" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>IT- equipment - switches</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10">
-        <v>1</v>
-      </c>
-      <c r="H10" s="10">
-        <v>1500</v>
-      </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10">
-        <f t="shared" si="3"/>
-        <v>1500</v>
-      </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="M10" s="13">
-        <v>40</v>
-      </c>
-      <c r="N10" s="10">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="10">
-        <v>13000</v>
-      </c>
-      <c r="B11" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>IT - equipment - end users (computers and laptops)</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10">
-        <v>8</v>
-      </c>
-      <c r="H11" s="10">
-        <v>1000</v>
-      </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10">
-        <f t="shared" si="3"/>
-        <v>8000</v>
-      </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="M11" s="13">
-        <v>150</v>
-      </c>
-      <c r="N11" s="10">
-        <f t="shared" si="1"/>
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="10">
-        <v>12000</v>
-      </c>
-      <c r="B12" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>IT - equipment - periphery (telephony and printers)</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10">
-        <v>1</v>
-      </c>
-      <c r="H12" s="10">
-        <v>1500</v>
-      </c>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10">
-        <f t="shared" si="3"/>
-        <v>1500</v>
-      </c>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="M12" s="13">
-        <v>30</v>
-      </c>
-      <c r="N12" s="10">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="10">
-        <v>12000</v>
-      </c>
-      <c r="B13" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>IT - equipment - periphery (telephony and printers)</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10">
-        <v>1</v>
-      </c>
-      <c r="H13" s="10">
-        <v>75</v>
-      </c>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10">
-        <f t="shared" si="3"/>
-        <v>75</v>
-      </c>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="M13" s="13">
-        <v>10</v>
-      </c>
-      <c r="N13" s="10">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="10">
-        <v>11000</v>
-      </c>
-      <c r="B14" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>IT- equipment - switches</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10">
-        <v>1</v>
-      </c>
-      <c r="H14" s="10">
-        <v>1500</v>
-      </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10">
-        <f t="shared" si="3"/>
-        <v>1500</v>
-      </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="M14" s="13">
-        <v>40</v>
-      </c>
-      <c r="N14" s="10">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="10">
-        <v>13000</v>
-      </c>
-      <c r="B15" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>IT - equipment - end users (computers and laptops)</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10">
-        <v>10</v>
-      </c>
-      <c r="H15" s="10">
-        <v>1000</v>
-      </c>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10">
-        <f t="shared" si="3"/>
-        <v>10000</v>
-      </c>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="M15" s="13">
-        <v>150</v>
-      </c>
-      <c r="N15" s="10">
-        <f t="shared" si="1"/>
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="10">
-        <v>12000</v>
-      </c>
-      <c r="B16" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>IT - equipment - periphery (telephony and printers)</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>24</v>
       </c>
       <c r="F16" s="10"/>
       <c r="G16" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H16" s="10">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="I16" s="10"/>
       <c r="J16" s="10">
-        <f t="shared" si="3"/>
-        <v>75</v>
+        <f>G16*H16</f>
+        <v>5000</v>
       </c>
       <c r="K16" s="10"/>
       <c r="L16" s="10" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="M16" s="13">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="N16" s="10">
-        <f t="shared" si="1"/>
-        <v>10</v>
+        <f t="shared" ref="N16:N55" si="1">M16*G16</f>
+        <v>750</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1659,10 +1391,10 @@
         <v>16</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="10">
@@ -1673,12 +1405,12 @@
       </c>
       <c r="I17" s="10"/>
       <c r="J17" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J17" si="2">G17*H17</f>
         <v>1500</v>
       </c>
       <c r="K17" s="10"/>
       <c r="L17" s="10" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="M17" s="13">
         <v>30</v>
@@ -1690,84 +1422,84 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="B18" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>IT- equipment - switches</v>
+        <v>IT - equipment - periphery (telephony and printers)</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="10">
         <v>1</v>
       </c>
       <c r="H18" s="10">
-        <v>1500</v>
+        <v>75</v>
       </c>
       <c r="I18" s="10"/>
       <c r="J18" s="10">
-        <f>G18*H18</f>
-        <v>1500</v>
+        <f t="shared" ref="J18:J55" si="3">G18*H18</f>
+        <v>75</v>
       </c>
       <c r="K18" s="10"/>
       <c r="L18" s="10" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="M18" s="13">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="N18" s="10">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
-        <v>13000</v>
+        <v>11000</v>
       </c>
       <c r="B19" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>IT - equipment - end users (computers and laptops)</v>
+        <v>IT- equipment - switches</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H19" s="10">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I19" s="10"/>
       <c r="J19" s="10">
         <f t="shared" si="3"/>
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="K19" s="10"/>
       <c r="L19" s="10" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="M19" s="13">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="N19" s="10">
         <f t="shared" si="1"/>
-        <v>1500</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1782,197 +1514,197 @@
         <v>16</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="10">
         <v>1</v>
       </c>
       <c r="H20" s="10">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="I20" s="10"/>
       <c r="J20" s="10">
-        <f t="shared" ref="J20:J21" si="4">G20*H20</f>
-        <v>75</v>
+        <f t="shared" si="3"/>
+        <v>150</v>
       </c>
       <c r="K20" s="10"/>
       <c r="L20" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="M20" s="13">
         <v>35</v>
       </c>
-      <c r="M20" s="13">
-        <v>10</v>
-      </c>
       <c r="N20" s="10">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="B21" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>IT - equipment - periphery (telephony and printers)</v>
+        <v>IT - equipment - routers</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="10">
         <v>1</v>
       </c>
       <c r="H21" s="10">
-        <v>1500</v>
+        <v>150</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" s="10">
-        <f t="shared" si="4"/>
-        <v>1500</v>
+        <f t="shared" si="3"/>
+        <v>150</v>
       </c>
       <c r="K21" s="10"/>
       <c r="L21" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="M21" s="13">
         <v>35</v>
       </c>
-      <c r="M21" s="13">
-        <v>30</v>
-      </c>
       <c r="N21" s="10">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="B22" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>IT- equipment - switches</v>
+        <v>IT - equipment - routers</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="10">
         <v>1</v>
       </c>
       <c r="H22" s="10">
-        <v>1500</v>
+        <v>150</v>
       </c>
       <c r="I22" s="10"/>
       <c r="J22" s="10">
-        <f>G22*H22</f>
-        <v>1500</v>
+        <f t="shared" si="3"/>
+        <v>150</v>
       </c>
       <c r="K22" s="10"/>
       <c r="L22" s="10" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="M22" s="13">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="N22" s="10">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="10">
-        <v>13000</v>
+        <v>11000</v>
       </c>
       <c r="B23" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>IT - equipment - end users (computers and laptops)</v>
+        <v>IT- equipment - switches</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H23" s="10">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I23" s="10"/>
       <c r="J23" s="10">
         <f t="shared" si="3"/>
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="K23" s="10"/>
       <c r="L23" s="10" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="M23" s="13">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="N23" s="10">
         <f t="shared" si="1"/>
-        <v>1500</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="B24" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>IT - equipment - periphery (telephony and printers)</v>
+        <v>IT - equipment - end users (computers and laptops)</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="10">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H24" s="10">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="I24" s="10"/>
       <c r="J24" s="10">
         <f t="shared" si="3"/>
-        <v>75</v>
+        <v>8000</v>
       </c>
       <c r="K24" s="10"/>
       <c r="L24" s="10" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="M24" s="13">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="N24" s="10">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -1987,7 +1719,7 @@
         <v>16</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>41</v>
@@ -2006,7 +1738,7 @@
       </c>
       <c r="K25" s="10"/>
       <c r="L25" s="10" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="M25" s="13">
         <v>30</v>
@@ -2018,125 +1750,125 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="B26" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>IT- equipment - switches</v>
+        <v>IT - equipment - periphery (telephony and printers)</v>
       </c>
       <c r="C26" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="F26" s="10"/>
       <c r="G26" s="10">
         <v>1</v>
       </c>
       <c r="H26" s="10">
-        <v>1500</v>
+        <v>75</v>
       </c>
       <c r="I26" s="10"/>
       <c r="J26" s="10">
-        <f>G26*H26</f>
-        <v>1500</v>
+        <f t="shared" si="3"/>
+        <v>75</v>
       </c>
       <c r="K26" s="10"/>
       <c r="L26" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="M26" s="13">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="N26" s="10">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
-        <v>13000</v>
+        <v>11000</v>
       </c>
       <c r="B27" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>IT - equipment - end users (computers and laptops)</v>
+        <v>IT- equipment - switches</v>
       </c>
       <c r="C27" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F27" s="10"/>
       <c r="G27" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H27" s="10">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" s="10">
         <f t="shared" si="3"/>
-        <v>5000</v>
+        <v>1500</v>
       </c>
       <c r="K27" s="10"/>
       <c r="L27" s="10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M27" s="13">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="N27" s="10">
         <f t="shared" si="1"/>
-        <v>750</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="B28" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>IT - equipment - periphery (telephony and printers)</v>
+        <v>IT - equipment - end users (computers and laptops)</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F28" s="10"/>
       <c r="G28" s="10">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H28" s="10">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="I28" s="10"/>
       <c r="J28" s="10">
         <f t="shared" si="3"/>
-        <v>75</v>
+        <v>10000</v>
       </c>
       <c r="K28" s="10"/>
       <c r="L28" s="10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M28" s="13">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="N28" s="10">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -2151,74 +1883,74 @@
         <v>16</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F29" s="10"/>
       <c r="G29" s="10">
         <v>1</v>
       </c>
       <c r="H29" s="10">
-        <v>1500</v>
+        <v>75</v>
       </c>
       <c r="I29" s="10"/>
       <c r="J29" s="10">
         <f t="shared" si="3"/>
-        <v>1500</v>
+        <v>75</v>
       </c>
       <c r="K29" s="10"/>
       <c r="L29" s="10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M29" s="13">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="N29" s="10">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="B30" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>IT - equipment - routers</v>
+        <v>IT - equipment - periphery (telephony and printers)</v>
       </c>
       <c r="C30" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F30" s="10"/>
       <c r="G30" s="10">
         <v>1</v>
       </c>
       <c r="H30" s="10">
-        <v>100</v>
+        <v>1500</v>
       </c>
       <c r="I30" s="10"/>
       <c r="J30" s="10">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>1500</v>
       </c>
       <c r="K30" s="10"/>
       <c r="L30" s="10" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="M30" s="13">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="N30" s="10">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -2233,10 +1965,10 @@
         <v>16</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F31" s="10"/>
       <c r="G31" s="10">
@@ -2252,7 +1984,7 @@
       </c>
       <c r="K31" s="10"/>
       <c r="L31" s="10" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="M31" s="13">
         <v>40</v>
@@ -2264,191 +1996,188 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="B32" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>IT - equipment - servers</v>
+        <v>IT - equipment - end users (computers and laptops)</v>
       </c>
       <c r="C32" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="F32" s="10"/>
       <c r="G32" s="10">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H32" s="10">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="I32" s="10"/>
       <c r="J32" s="10">
         <f t="shared" si="3"/>
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="K32" s="10"/>
       <c r="L32" s="10" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="M32" s="13">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N32" s="10">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="B33" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>IT - equipment - servers</v>
+        <v>IT - equipment - periphery (telephony and printers)</v>
       </c>
       <c r="C33" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="10">
         <v>1</v>
       </c>
       <c r="H33" s="10">
-        <v>2000</v>
+        <v>75</v>
       </c>
       <c r="I33" s="10"/>
       <c r="J33" s="10">
-        <f t="shared" si="3"/>
-        <v>2000</v>
+        <f t="shared" ref="J33:J34" si="4">G33*H33</f>
+        <v>75</v>
       </c>
       <c r="K33" s="10"/>
       <c r="L33" s="10" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="M33" s="13">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="N33" s="10">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
-        <v>14000</v>
+        <v>12000</v>
       </c>
       <c r="B34" s="10" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">IT - equipment - cables </v>
+        <v>IT - equipment - periphery (telephony and printers)</v>
       </c>
       <c r="C34" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34" s="10">
-        <f>10*10*G34</f>
-        <v>200</v>
+        <v>1500</v>
       </c>
       <c r="I34" s="10"/>
       <c r="J34" s="10">
-        <f t="shared" si="3"/>
-        <v>400</v>
+        <f t="shared" si="4"/>
+        <v>1500</v>
       </c>
       <c r="K34" s="10"/>
       <c r="L34" s="10" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="M34" s="13">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N34" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
-        <v>14000</v>
+        <v>11000</v>
       </c>
       <c r="B35" s="10" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">IT - equipment - cables </v>
+        <v>IT- equipment - switches</v>
       </c>
       <c r="C35" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="10">
-        <f>62+7</f>
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="H35" s="10">
-        <f>2*2*G35</f>
-        <v>276</v>
+        <v>1500</v>
       </c>
       <c r="I35" s="10"/>
       <c r="J35" s="10">
-        <f t="shared" si="3"/>
-        <v>19044</v>
+        <f>G35*H35</f>
+        <v>1500</v>
       </c>
       <c r="K35" s="10"/>
       <c r="L35" s="10" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="M35" s="13">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="N35" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
-        <v>10000</v>
+        <v>13000</v>
       </c>
       <c r="B36" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>IT - equipment - routers</v>
+        <v>IT - equipment - end users (computers and laptops)</v>
       </c>
       <c r="C36" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="10">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H36" s="10">
         <v>1000</v>
@@ -2456,493 +2185,893 @@
       <c r="I36" s="10"/>
       <c r="J36" s="10">
         <f t="shared" si="3"/>
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K36" s="10"/>
       <c r="L36" s="10" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="M36" s="13">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="N36" s="10">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
-        <v>15001</v>
+        <v>12000</v>
       </c>
       <c r="B37" s="10" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">Other </v>
+        <v>IT - equipment - periphery (telephony and printers)</v>
       </c>
       <c r="C37" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H37" s="10">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="I37" s="10"/>
       <c r="J37" s="10">
         <f t="shared" si="3"/>
-        <v>4000</v>
+        <v>75</v>
       </c>
       <c r="K37" s="10"/>
       <c r="L37" s="10" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="M37" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N37" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="B38" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>IT - equipment - servers</v>
+        <v>IT - equipment - periphery (telephony and printers)</v>
       </c>
       <c r="C38" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="10">
         <v>1</v>
       </c>
       <c r="H38" s="10">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I38" s="10"/>
       <c r="J38" s="10">
         <f t="shared" si="3"/>
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="K38" s="10"/>
       <c r="L38" s="10" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M38" s="13">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="N38" s="10">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
+      <c r="A39" s="10">
+        <v>11000</v>
+      </c>
+      <c r="B39" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>IT- equipment - switches</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>44</v>
+      </c>
       <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
+      <c r="G39" s="10">
+        <v>1</v>
+      </c>
+      <c r="H39" s="10">
+        <v>1500</v>
+      </c>
       <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
+      <c r="J39" s="10">
+        <f>G39*H39</f>
+        <v>1500</v>
+      </c>
       <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
-      <c r="M39" s="13"/>
-      <c r="N39" s="10"/>
+      <c r="L39" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="M39" s="13">
+        <v>40</v>
+      </c>
+      <c r="N39" s="10">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="10"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
+      <c r="A40" s="10">
+        <v>13000</v>
+      </c>
+      <c r="B40" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>IT - equipment - end users (computers and laptops)</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>27</v>
+      </c>
       <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
+      <c r="G40" s="10">
+        <v>5</v>
+      </c>
+      <c r="H40" s="10">
+        <v>1000</v>
+      </c>
       <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
+      <c r="J40" s="10">
+        <f t="shared" si="3"/>
+        <v>5000</v>
+      </c>
       <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-      <c r="M40" s="13"/>
-      <c r="N40" s="10"/>
+      <c r="L40" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="M40" s="13">
+        <v>150</v>
+      </c>
+      <c r="N40" s="10">
+        <f t="shared" si="1"/>
+        <v>750</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
-        <v>15001</v>
+        <v>12000</v>
       </c>
       <c r="B41" s="10" t="str">
-        <f>LOOKUP(A41,$B$51:$B$57,$C$51:$C$57)</f>
-        <v xml:space="preserve">Other </v>
+        <f t="shared" si="0"/>
+        <v>IT - equipment - periphery (telephony and printers)</v>
       </c>
       <c r="C41" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="F41" s="10"/>
       <c r="G41" s="10">
         <v>1</v>
       </c>
-      <c r="H41" s="10"/>
+      <c r="H41" s="10">
+        <v>75</v>
+      </c>
       <c r="I41" s="10"/>
       <c r="J41" s="10">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K41" s="10"/>
       <c r="L41" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="M41" s="13">
+        <v>10</v>
+      </c>
+      <c r="N41" s="10">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" s="10">
+        <v>12000</v>
+      </c>
+      <c r="B42" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>IT - equipment - periphery (telephony and printers)</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10">
+        <v>1</v>
+      </c>
+      <c r="H42" s="10">
+        <v>1500</v>
+      </c>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="K42" s="10"/>
+      <c r="L42" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="M42" s="13">
+        <v>30</v>
+      </c>
+      <c r="N42" s="10">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43" s="10">
+        <v>10000</v>
+      </c>
+      <c r="B43" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>IT - equipment - routers</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10">
+        <v>1</v>
+      </c>
+      <c r="H43" s="10">
+        <v>100</v>
+      </c>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M43" s="13">
+        <v>50</v>
+      </c>
+      <c r="N43" s="10">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44" s="10">
+        <v>11000</v>
+      </c>
+      <c r="B44" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>IT- equipment - switches</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F44" s="10"/>
+      <c r="G44" s="10">
+        <v>2</v>
+      </c>
+      <c r="H44" s="10">
+        <v>1500</v>
+      </c>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10">
+        <f>G44*H44</f>
+        <v>3000</v>
+      </c>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="M44" s="13">
+        <v>40</v>
+      </c>
+      <c r="N44" s="10">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A45" s="10">
+        <v>15000</v>
+      </c>
+      <c r="B45" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>IT - equipment - servers</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10">
+        <v>1</v>
+      </c>
+      <c r="H45" s="10">
+        <v>2000</v>
+      </c>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10">
+        <f t="shared" si="3"/>
+        <v>2000</v>
+      </c>
+      <c r="K45" s="10"/>
+      <c r="L45" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="M45" s="13">
+        <v>200</v>
+      </c>
+      <c r="N45" s="10">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A46" s="10">
+        <v>15000</v>
+      </c>
+      <c r="B46" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>IT - equipment - servers</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10">
+        <v>1</v>
+      </c>
+      <c r="H46" s="10">
+        <v>2000</v>
+      </c>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10">
+        <f t="shared" si="3"/>
+        <v>2000</v>
+      </c>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="M46" s="13">
+        <v>200</v>
+      </c>
+      <c r="N46" s="10">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A47" s="10">
+        <v>14000</v>
+      </c>
+      <c r="B47" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">IT - equipment - cables </v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F47" s="10"/>
+      <c r="G47" s="10">
+        <v>2</v>
+      </c>
+      <c r="H47" s="10">
+        <f>10*10*G47</f>
+        <v>200</v>
+      </c>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10">
+        <f t="shared" si="3"/>
+        <v>400</v>
+      </c>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="M47" s="13">
+        <v>0</v>
+      </c>
+      <c r="N47" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A48" s="10">
+        <v>14000</v>
+      </c>
+      <c r="B48" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">IT - equipment - cables </v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10">
+        <v>70</v>
+      </c>
+      <c r="H48" s="10">
+        <f>2*2*G48</f>
+        <v>280</v>
+      </c>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10">
+        <f t="shared" si="3"/>
+        <v>19600</v>
+      </c>
+      <c r="K48" s="10"/>
+      <c r="L48" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="M48" s="13">
+        <v>0</v>
+      </c>
+      <c r="N48" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>10000</v>
+      </c>
+      <c r="B49" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>IT - equipment - routers</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10">
+        <v>1</v>
+      </c>
+      <c r="H49" s="10">
+        <v>1000</v>
+      </c>
+      <c r="I49" s="10"/>
+      <c r="J49" s="10">
+        <f t="shared" si="3"/>
+        <v>1000</v>
+      </c>
+      <c r="K49" s="10"/>
+      <c r="L49" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="M49" s="13">
+        <v>40</v>
+      </c>
+      <c r="N49" s="10">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>15001</v>
+      </c>
+      <c r="B50" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Other </v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F50" s="10"/>
+      <c r="G50" s="10">
+        <v>4</v>
+      </c>
+      <c r="H50" s="10">
+        <v>1000</v>
+      </c>
+      <c r="I50" s="10"/>
+      <c r="J50" s="10">
+        <f t="shared" si="3"/>
+        <v>4000</v>
+      </c>
+      <c r="K50" s="10"/>
+      <c r="L50" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="M50" s="13">
+        <v>0</v>
+      </c>
+      <c r="N50" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>15000</v>
+      </c>
+      <c r="B51" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>IT - equipment - servers</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10">
+        <v>1</v>
+      </c>
+      <c r="H51" s="10">
+        <v>2000</v>
+      </c>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10">
+        <f t="shared" si="3"/>
+        <v>2000</v>
+      </c>
+      <c r="K51" s="10"/>
+      <c r="L51" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="M51" s="13">
+        <v>200</v>
+      </c>
+      <c r="N51" s="10">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>10000</v>
+      </c>
+      <c r="B52" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>IT - equipment - routers</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F52" s="10"/>
+      <c r="G52" s="10">
+        <v>1</v>
+      </c>
+      <c r="H52" s="10">
+        <v>1180</v>
+      </c>
+      <c r="I52" s="10"/>
+      <c r="J52" s="10">
+        <f t="shared" si="3"/>
+        <v>1180</v>
+      </c>
+      <c r="K52" s="10"/>
+      <c r="L52" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="M52" s="13">
+        <v>48</v>
+      </c>
+      <c r="N52" s="10">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>15000</v>
+      </c>
+      <c r="B53" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>IT - equipment - servers</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F53" s="10"/>
+      <c r="G53" s="10">
+        <v>1</v>
+      </c>
+      <c r="H53" s="10">
+        <v>2000</v>
+      </c>
+      <c r="I53" s="10"/>
+      <c r="J53" s="10">
+        <f t="shared" si="3"/>
+        <v>2000</v>
+      </c>
+      <c r="K53" s="10"/>
+      <c r="L53" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="M53" s="13">
+        <v>200</v>
+      </c>
+      <c r="N53" s="10">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A54" s="10">
+        <v>15000</v>
+      </c>
+      <c r="B54" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>IT - equipment - servers</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10">
+        <v>1</v>
+      </c>
+      <c r="H54" s="10">
+        <v>2000</v>
+      </c>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10">
+        <f t="shared" si="3"/>
+        <v>2000</v>
+      </c>
+      <c r="K54" s="10"/>
+      <c r="L54" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="M54" s="13">
+        <v>200</v>
+      </c>
+      <c r="N54" s="10">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A55" s="10">
+        <v>15001</v>
+      </c>
+      <c r="B55" s="10" t="str">
+        <f>LOOKUP(A55,$B$4:$B$10,$C$4:$C$10)</f>
+        <v xml:space="preserve">Other </v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10">
+        <v>1</v>
+      </c>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="10"/>
+      <c r="L55" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="M41" s="13">
+      <c r="M55" s="13">
         <v>500</v>
       </c>
-      <c r="N41" s="10">
+      <c r="N55" s="10">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M43">
-        <f>SUM(M3:M42)</f>
-        <v>2715</v>
-      </c>
-      <c r="N43">
-        <f>SUM(N3:N42)</f>
-        <v>9015</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="49" spans="2:15" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C49" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D49" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="E49" s="35"/>
-      <c r="F49" s="36"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="I49" s="35"/>
-      <c r="J49" s="36"/>
-      <c r="K49" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="L49" s="32"/>
-      <c r="M49" s="33"/>
-    </row>
-    <row r="50" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B50" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C50" s="4"/>
-      <c r="D50" s="37">
-        <f>SUM(D51:F57)</f>
-        <v>98944</v>
-      </c>
-      <c r="E50" s="38"/>
-      <c r="F50" s="39"/>
-      <c r="G50" s="19"/>
-      <c r="H50" s="40" t="s">
-        <v>19</v>
-      </c>
-      <c r="I50" s="41"/>
-      <c r="J50" s="42"/>
-      <c r="K50" s="37">
-        <f>SUM(K51:M57)</f>
-        <v>98944</v>
-      </c>
-      <c r="L50" s="38"/>
-      <c r="M50" s="39"/>
-    </row>
-    <row r="51" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B51" s="1">
-        <v>10000</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D51" s="23">
-        <f t="shared" ref="D51:D57" si="5">SUMIF($A:$A,$B51,$J:$J)</f>
-        <v>1400</v>
-      </c>
-      <c r="E51" s="24"/>
-      <c r="F51" s="25"/>
-      <c r="G51" s="20"/>
-      <c r="H51" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="I51" s="24"/>
-      <c r="J51" s="25"/>
-      <c r="K51" s="23">
-        <f t="shared" ref="K51:K57" si="6">SUMIF($D:$D,H51,$J:$J)</f>
-        <v>8075</v>
-      </c>
-      <c r="L51" s="24"/>
-      <c r="M51" s="25"/>
-      <c r="N51" s="44"/>
-      <c r="O51" s="44"/>
-    </row>
-    <row r="52" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B52" s="1">
-        <v>11000</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D52" s="23">
-        <f t="shared" si="5"/>
-        <v>10500</v>
-      </c>
-      <c r="E52" s="24"/>
-      <c r="F52" s="25"/>
-      <c r="G52" s="20"/>
-      <c r="H52" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="I52" s="24"/>
-      <c r="J52" s="25"/>
-      <c r="K52" s="23">
-        <f t="shared" si="6"/>
-        <v>11075</v>
-      </c>
-      <c r="L52" s="24"/>
-      <c r="M52" s="25"/>
-      <c r="N52" s="44"/>
-      <c r="O52" s="44"/>
-    </row>
-    <row r="53" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B53" s="1">
-        <v>12000</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D53" s="23">
-        <f t="shared" si="5"/>
-        <v>9600</v>
-      </c>
-      <c r="E53" s="24"/>
-      <c r="F53" s="25"/>
-      <c r="G53" s="20"/>
-      <c r="H53" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I53" s="24"/>
-      <c r="J53" s="25"/>
-      <c r="K53" s="23">
-        <f t="shared" si="6"/>
-        <v>13075</v>
-      </c>
-      <c r="L53" s="24"/>
-      <c r="M53" s="25"/>
-      <c r="N53" s="44"/>
-      <c r="O53" s="44"/>
-    </row>
-    <row r="54" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B54" s="1">
-        <v>13000</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D54" s="23">
-        <f t="shared" si="5"/>
-        <v>48000</v>
-      </c>
-      <c r="E54" s="24"/>
-      <c r="F54" s="25"/>
-      <c r="G54" s="20"/>
-      <c r="H54" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="I54" s="24"/>
-      <c r="J54" s="25"/>
-      <c r="K54" s="23">
-        <f t="shared" si="6"/>
-        <v>13075</v>
-      </c>
-      <c r="L54" s="24"/>
-      <c r="M54" s="25"/>
-      <c r="N54" s="44"/>
-      <c r="O54" s="44"/>
-    </row>
-    <row r="55" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B55" s="1">
-        <v>14000</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D55" s="23">
-        <f t="shared" si="5"/>
-        <v>19444</v>
-      </c>
-      <c r="E55" s="24"/>
-      <c r="F55" s="25"/>
-      <c r="G55" s="20"/>
-      <c r="H55" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="I55" s="24"/>
-      <c r="J55" s="25"/>
-      <c r="K55" s="23">
-        <f t="shared" si="6"/>
-        <v>13075</v>
-      </c>
-      <c r="L55" s="24"/>
-      <c r="M55" s="25"/>
-      <c r="N55" s="44"/>
-      <c r="O55" s="44"/>
-    </row>
-    <row r="56" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B56" s="1">
-        <v>15000</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D56" s="23">
-        <f t="shared" si="5"/>
-        <v>6000</v>
-      </c>
-      <c r="E56" s="24"/>
-      <c r="F56" s="25"/>
-      <c r="G56" s="20"/>
-      <c r="H56" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="I56" s="24"/>
-      <c r="J56" s="25"/>
-      <c r="K56" s="23">
-        <f t="shared" si="6"/>
-        <v>12075</v>
-      </c>
-      <c r="L56" s="24"/>
-      <c r="M56" s="25"/>
-      <c r="N56" s="44"/>
-      <c r="O56" s="44"/>
-    </row>
-    <row r="57" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="1">
-        <v>15001</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D57" s="23">
-        <f t="shared" si="5"/>
-        <v>4000</v>
-      </c>
-      <c r="E57" s="24"/>
-      <c r="F57" s="25"/>
-      <c r="G57" s="20"/>
-      <c r="H57" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="I57" s="24"/>
-      <c r="J57" s="25"/>
-      <c r="K57" s="23">
-        <f t="shared" si="6"/>
-        <v>28494</v>
-      </c>
-      <c r="L57" s="24"/>
-      <c r="M57" s="25"/>
-      <c r="N57" s="44"/>
-      <c r="O57" s="44"/>
-    </row>
-    <row r="58" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="30"/>
-      <c r="D58" s="26">
-        <f>SUM(D51:F57)</f>
-        <v>98944</v>
-      </c>
-      <c r="E58" s="27"/>
-      <c r="F58" s="28"/>
-      <c r="G58" s="21"/>
-      <c r="H58" s="5"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="15"/>
-      <c r="K58" s="26">
-        <f>SUM(K50)</f>
-        <v>98944</v>
-      </c>
-      <c r="L58" s="27"/>
-      <c r="M58" s="28"/>
-      <c r="O58" s="22">
-        <f>K58-D58</f>
-        <v>0</v>
-      </c>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M57">
+        <f>SUM(M16:M56)</f>
+        <v>3163</v>
+      </c>
+      <c r="N57">
+        <f>SUM(N16:N56)</f>
+        <v>9503</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="G63" s="18"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="G64" s="19"/>
+    </row>
+    <row r="65" spans="7:15" x14ac:dyDescent="0.3">
+      <c r="G65" s="20"/>
+      <c r="N65" s="44"/>
+      <c r="O65" s="44"/>
+    </row>
+    <row r="66" spans="7:15" x14ac:dyDescent="0.3">
+      <c r="G66" s="20"/>
+      <c r="N66" s="44"/>
+      <c r="O66" s="44"/>
+    </row>
+    <row r="67" spans="7:15" x14ac:dyDescent="0.3">
+      <c r="G67" s="20"/>
+      <c r="N67" s="44"/>
+      <c r="O67" s="44"/>
+    </row>
+    <row r="68" spans="7:15" x14ac:dyDescent="0.3">
+      <c r="G68" s="20"/>
+      <c r="N68" s="44"/>
+      <c r="O68" s="44"/>
+    </row>
+    <row r="69" spans="7:15" x14ac:dyDescent="0.3">
+      <c r="G69" s="20"/>
+      <c r="N69" s="44"/>
+      <c r="O69" s="44"/>
+    </row>
+    <row r="70" spans="7:15" x14ac:dyDescent="0.3">
+      <c r="G70" s="20"/>
+      <c r="N70" s="44"/>
+      <c r="O70" s="44"/>
+    </row>
+    <row r="71" spans="7:15" x14ac:dyDescent="0.3">
+      <c r="G71" s="20"/>
+      <c r="N71" s="44"/>
+      <c r="O71" s="44"/>
+    </row>
+    <row r="72" spans="7:15" x14ac:dyDescent="0.3">
+      <c r="G72" s="21"/>
     </row>
   </sheetData>
+  <autoFilter ref="A15:O53" xr:uid="{032A4627-C2A2-4924-A3A7-17B2D83EA8DD}"/>
   <mergeCells count="37">
-    <mergeCell ref="H49:J49"/>
-    <mergeCell ref="N53:O53"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="N51:O51"/>
-    <mergeCell ref="H57:J57"/>
-    <mergeCell ref="H56:J56"/>
-    <mergeCell ref="H55:J55"/>
-    <mergeCell ref="H54:J54"/>
-    <mergeCell ref="H53:J53"/>
-    <mergeCell ref="H52:J52"/>
-    <mergeCell ref="H51:J51"/>
-    <mergeCell ref="K56:M56"/>
-    <mergeCell ref="N57:O57"/>
-    <mergeCell ref="N56:O56"/>
-    <mergeCell ref="N55:O55"/>
-    <mergeCell ref="N54:O54"/>
-    <mergeCell ref="K49:M49"/>
-    <mergeCell ref="K52:M52"/>
-    <mergeCell ref="K53:M53"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="K50:M50"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="K51:M51"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="K55:M55"/>
-    <mergeCell ref="K54:M54"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="K57:M57"/>
-    <mergeCell ref="K58:M58"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="N71:O71"/>
+    <mergeCell ref="N70:O70"/>
+    <mergeCell ref="N69:O69"/>
+    <mergeCell ref="N68:O68"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="N67:O67"/>
+    <mergeCell ref="N66:O66"/>
+    <mergeCell ref="N65:O65"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
